--- a/data/trans_bre/P1421-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1421-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>198,62%</t>
+          <t>239,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 5,09</t>
+          <t>-1,77; 5,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,38</t>
+          <t>2,97; 10,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,11</t>
+          <t>4,52; 11,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 10,96</t>
+          <t>4,16; 11,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 259,24</t>
+          <t>-44,29; 306,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,45; 1450,45</t>
+          <t>79,79; 1923,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>132,84; 2822,53</t>
+          <t>149,55; 3143,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,09; 533,94</t>
+          <t>75,5; 672,91</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>111,62%</t>
+          <t>104,8%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,41</t>
+          <t>5,44; 10,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,1</t>
+          <t>1,77; 6,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,93</t>
+          <t>1,33; 4,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 11,18</t>
+          <t>3,15; 10,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>328,77; 4099,21</t>
+          <t>287,48; 3691,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,75; 1584,94</t>
+          <t>38,57; 1845,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,54; 2389,44</t>
+          <t>65,9; 2622,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,39; 227,54</t>
+          <t>32,46; 229,92</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>153,51%</t>
+          <t>161,02%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,86</t>
+          <t>-0,34; 5,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,46</t>
+          <t>0,27; 5,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,12</t>
+          <t>1,62; 6,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 11,33</t>
+          <t>4,35; 11,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 479,0</t>
+          <t>-25,55; 560,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 811,14</t>
+          <t>-19,12; 685,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,01; 365,95</t>
+          <t>59,06; 362,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>123,31%</t>
+          <t>244,93%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,88</t>
+          <t>0,03; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 10,85</t>
+          <t>4,19; 10,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,1</t>
+          <t>2,84; 9,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,3</t>
+          <t>2,46; 7,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 599,52</t>
+          <t>-12,03; 592,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>122,3; 1337,01</t>
+          <t>136,2; 1388,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,17; 1074,61</t>
+          <t>87,46; 856,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 413,8</t>
+          <t>48,16; 688,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>124,83%</t>
+          <t>130,04%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 5,03</t>
+          <t>-0,9; 4,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,42</t>
+          <t>5,39; 13,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,28</t>
+          <t>2,47; 11,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,86</t>
+          <t>2,45; 10,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>145,56; —</t>
+          <t>157,87; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,9; 1225,14</t>
+          <t>33,4; 1076,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,59; 302,47</t>
+          <t>35,06; 380,9</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>128,04%</t>
+          <t>134,45%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,47</t>
+          <t>-1,32; 6,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,89</t>
+          <t>0,08; 6,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,46</t>
+          <t>0,6; 7,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 12,63</t>
+          <t>4,33; 12,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 319,79</t>
+          <t>-33,32; 295,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 788,28</t>
+          <t>-8,99; 799,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 811,91</t>
+          <t>-2,19; 749,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,18; 267,15</t>
+          <t>48,81; 285,17</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>9,45</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>127,98%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,97</t>
+          <t>0,26; 4,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,07</t>
+          <t>1,22; 5,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,74</t>
+          <t>1,27; 5,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 11,24</t>
+          <t>5,84; 12,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 362,28</t>
+          <t>0,29; 334,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,89; 645,4</t>
+          <t>34,98; 648,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,92; 395,14</t>
+          <t>36,41; 416,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 169,57</t>
+          <t>62,14; 224,51</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>469,45%</t>
+          <t>280,29%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,29</t>
+          <t>1,52; 6,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,04</t>
+          <t>1,42; 4,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,58</t>
+          <t>1,46; 4,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,63</t>
+          <t>2,33; 5,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,53; 206,37</t>
+          <t>27,88; 209,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,42; 1872,94</t>
+          <t>116,81; 2227,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,81; 747,13</t>
+          <t>82,63; 707,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>177,99; 1543,17</t>
+          <t>101,87; 688,34</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>139,14%</t>
+          <t>149,38%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,37</t>
+          <t>2,45; 4,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,05</t>
+          <t>3,31; 5,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,04</t>
+          <t>3,15; 4,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,69</t>
+          <t>5,55; 7,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,9; 221,76</t>
+          <t>86,83; 214,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>223,98; 566,26</t>
+          <t>219,39; 524,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>184,12; 429,99</t>
+          <t>183,57; 449,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>89,21; 210,62</t>
+          <t>105,0; 201,19</t>
         </is>
       </c>
     </row>
